--- a/docs/List Menu.xlsx
+++ b/docs/List Menu.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="138">
   <si>
     <t>Level</t>
   </si>
@@ -430,6 +430,9 @@
   </si>
   <si>
     <t>/audit-trail</t>
+  </si>
+  <si>
+    <t>TAKE</t>
   </si>
 </sst>
 </file>
@@ -826,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
@@ -835,7 +838,7 @@
     <col min="4" max="4" width="45.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="37.5" customHeight="1">
+    <row r="1" spans="1:5" ht="37.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -849,7 +852,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -863,7 +866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -877,7 +880,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -890,8 +893,11 @@
       <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -905,7 +911,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
@@ -919,7 +925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
@@ -933,7 +939,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -946,8 +952,11 @@
       <c r="D8" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
@@ -960,8 +969,11 @@
       <c r="D9" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -974,8 +986,11 @@
       <c r="D10" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -988,8 +1003,11 @@
       <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -1002,8 +1020,11 @@
       <c r="D12" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
@@ -1016,8 +1037,11 @@
       <c r="D13" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
@@ -1030,8 +1054,11 @@
       <c r="D14" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
         <v>9</v>
       </c>
@@ -1044,8 +1071,11 @@
       <c r="D15" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
         <v>9</v>
       </c>
@@ -1058,8 +1088,11 @@
       <c r="D16" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
         <v>9</v>
       </c>
@@ -1072,8 +1105,11 @@
       <c r="D17" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
@@ -1086,8 +1122,11 @@
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
@@ -1100,8 +1139,11 @@
       <c r="D19" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
         <v>9</v>
       </c>
@@ -1114,8 +1156,11 @@
       <c r="D20" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
@@ -1128,8 +1173,11 @@
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
         <v>9</v>
       </c>
@@ -1142,8 +1190,11 @@
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
         <v>1</v>
       </c>
@@ -1157,7 +1208,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
         <v>1</v>
       </c>
@@ -1170,8 +1221,11 @@
       <c r="D24" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1238,11 @@
       <c r="D25" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
         <v>9</v>
       </c>
@@ -1199,7 +1256,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
         <v>9</v>
       </c>
@@ -1213,7 +1270,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
@@ -1227,7 +1284,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
         <v>9</v>
       </c>
@@ -1241,7 +1298,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
         <v>1</v>
       </c>
@@ -1255,7 +1312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
         <v>9</v>
       </c>
@@ -1269,7 +1326,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
         <v>1</v>
       </c>
@@ -1282,8 +1339,11 @@
       <c r="D32" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
         <v>9</v>
       </c>
@@ -1296,8 +1356,11 @@
       <c r="D33" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
         <v>62</v>
       </c>
@@ -1310,8 +1373,11 @@
       <c r="D34" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
         <v>62</v>
       </c>
@@ -1324,8 +1390,11 @@
       <c r="D35" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
         <v>62</v>
       </c>
@@ -1338,8 +1407,11 @@
       <c r="D36" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
         <v>9</v>
       </c>
@@ -1352,8 +1424,11 @@
       <c r="D37" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
         <v>62</v>
       </c>
@@ -1366,8 +1441,11 @@
       <c r="D38" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
         <v>62</v>
       </c>
@@ -1380,8 +1458,11 @@
       <c r="D39" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
         <v>1</v>
       </c>
@@ -1395,7 +1476,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
         <v>9</v>
       </c>
@@ -1409,7 +1490,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
         <v>9</v>
       </c>
@@ -1423,7 +1504,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
         <v>9</v>
       </c>
@@ -1437,7 +1518,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>1</v>
       </c>
@@ -1451,7 +1532,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:5">
       <c r="A45" s="2" t="s">
         <v>1</v>
       </c>
@@ -1465,7 +1546,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
         <v>9</v>
       </c>
@@ -1479,7 +1560,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
         <v>9</v>
       </c>
@@ -1493,7 +1574,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:5">
       <c r="A48" s="2" t="s">
         <v>1</v>
       </c>
